--- a/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:04</t>
+    <t xml:space="preserve">2026-09-09 22:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:01</t>
+    <t xml:space="preserve">2026-09-17 13:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1487986.88</v>
+        <v>1359459.5</v>
       </c>
     </row>
     <row r="3">
@@ -1115,26 +1115,26 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1085860</v>
+        <v>1487986.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1006140.5</v>
+        <v>1085860</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1359459.5</v>
+        <v>1006140.5</v>
       </c>
     </row>
     <row r="7">
@@ -1175,35 +1175,35 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1334637.75</v>
+        <v>1217673.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1487986.88</v>
+        <v>1359459.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1606571.88</v>
+        <v>1457645.12</v>
       </c>
     </row>
     <row r="5">
@@ -1241,101 +1241,101 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>968522</v>
+        <v>1334637.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1085860</v>
+        <v>1487986.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1158183.88</v>
+        <v>1606571.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>888122</v>
+        <v>968522</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1006140.5</v>
+        <v>1085860</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1076358.62</v>
+        <v>1158183.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1217673.75</v>
+        <v>888122</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1359459.5</v>
+        <v>1006140.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1457645.12</v>
+        <v>1076358.62</v>
       </c>
     </row>
     <row r="17">

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:33</t>
+    <t xml:space="preserve">2026-09-25 21:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -809,7 +809,7 @@
         <v>1079407.62</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>134244.63</v>
+        <v>134244.62</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>12.44</v>
@@ -855,7 +855,7 @@
         <v>1173733.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>137940.87</v>
+        <v>137940.88</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>11.75</v>
@@ -993,7 +993,7 @@
         <v>1334637.75</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>153349.13</v>
+        <v>153349.12</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>11.49</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_metropolitana.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:34</t>
+    <t xml:space="preserve">2026-10-05 07:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -594,7 +594,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1006140</v>
+        <v>1006141</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>888122</v>
@@ -728,10 +728,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1340178</v>
+        <v>1340179</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1601120</v>
+        <v>1601121</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>-16.3</v>
